--- a/Flight_Deals.xlsx
+++ b/Flight_Deals.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1181.8</v>
+        <v>1210.6</v>
       </c>
     </row>
     <row r="3">
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>547.28</v>
+        <v>425.88</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1636</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="5">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1197</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>450.6</v>
+        <v>459</v>
       </c>
     </row>
     <row r="7">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1227.2</v>
+        <v>1251.6</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>988.8</v>
+        <v>1011.2</v>
       </c>
     </row>
     <row r="9">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1459</v>
+        <v>1343.8</v>
       </c>
     </row>
     <row r="10">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2081</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="13">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2267</v>
+        <v>2742.8</v>
       </c>
     </row>
     <row r="15">
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1202.6</v>
+        <v>1336.6</v>
       </c>
     </row>
     <row r="16">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1383.8</v>
+        <v>1248.8</v>
       </c>
     </row>
     <row r="17">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1302.2</v>
+        <v>1221.2</v>
       </c>
     </row>
     <row r="18">
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2274.8</v>
+        <v>1648.8</v>
       </c>
     </row>
     <row r="19">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1663.6</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="20">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1667</v>
+        <v>1647.8</v>
       </c>
     </row>
     <row r="21">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1670</v>
+        <v>1730.6</v>
       </c>
     </row>
     <row r="22">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>354.6</v>
+        <v>392.4</v>
       </c>
     </row>
     <row r="24">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>537.6</v>
+        <v>594.2</v>
       </c>
     </row>
     <row r="25">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>417.6</v>
+        <v>439.8</v>
       </c>
     </row>
     <row r="26">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>543</v>
+        <v>642.4</v>
       </c>
     </row>
     <row r="27">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>344.4</v>
+        <v>505</v>
       </c>
     </row>
     <row r="28">
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>528.6</v>
+        <v>562</v>
       </c>
     </row>
     <row r="30">
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>456.4</v>
+        <v>491.2</v>
       </c>
     </row>
     <row r="31">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>269.04</v>
+        <v>390.92</v>
       </c>
     </row>
     <row r="32">
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>424.8</v>
+        <v>378.2</v>
       </c>
     </row>
     <row r="33">
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>610.26</v>
+        <v>680.0599999999999</v>
       </c>
     </row>
     <row r="34">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>424.6</v>
+        <v>791.6</v>
       </c>
     </row>
     <row r="35">
@@ -961,10 +961,8 @@
           <t>GOH</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>N/a</t>
-        </is>
+      <c r="C35" t="n">
+        <v>1832</v>
       </c>
     </row>
     <row r="36">
@@ -979,7 +977,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1160.2</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="37">
@@ -994,7 +992,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3067</v>
+        <v>533.6</v>
       </c>
     </row>
     <row r="38">
@@ -1009,7 +1007,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1704</v>
+        <v>1735.4</v>
       </c>
     </row>
     <row r="39">
@@ -1024,7 +1022,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1678.2</v>
+        <v>1798.2</v>
       </c>
     </row>
     <row r="40">
@@ -1039,7 +1037,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1509.4</v>
+        <v>1567.4</v>
       </c>
     </row>
     <row r="41">
@@ -1054,7 +1052,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>553.2</v>
+        <v>508.6</v>
       </c>
     </row>
     <row r="42">
@@ -1069,7 +1067,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>517</v>
+        <v>825.4</v>
       </c>
     </row>
     <row r="43">
@@ -1084,7 +1082,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2073.2</v>
+        <v>1988.6</v>
       </c>
     </row>
     <row r="44">
@@ -1099,7 +1097,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1126.6</v>
+        <v>1053.2</v>
       </c>
     </row>
     <row r="45">
@@ -1114,7 +1112,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>485.4</v>
+        <v>460.8</v>
       </c>
     </row>
     <row r="46">
@@ -1129,7 +1127,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1803.8</v>
+        <v>1777.4</v>
       </c>
     </row>
     <row r="47">
@@ -1144,7 +1142,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>482.8</v>
+        <v>465.6</v>
       </c>
     </row>
     <row r="48">
@@ -1159,7 +1157,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>399.4</v>
+        <v>476</v>
       </c>
     </row>
     <row r="49">
@@ -1174,7 +1172,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>416.8</v>
+        <v>465.2</v>
       </c>
     </row>
     <row r="50">
@@ -1189,7 +1187,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>409.4</v>
+        <v>447.8</v>
       </c>
     </row>
     <row r="51">
